--- a/per-stock/WULF/financials.xlsx
+++ b/per-stock/WULF/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11060288512</v>
+        <v>14360536064</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13745514496</v>
+        <v>17045762048</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>146.36066</v>
+        <v>156.64865</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65.81076</v>
+        <v>85.447845</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -713,11 +722,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-284243616</v>
+        <v>-1686714000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.32</v>
+        <v>28.98</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D53</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C53</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B53</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B54:E54)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D51</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C51</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B51</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B52:E52)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D44</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C44</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B44</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B45:E45)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1817,13 +2297,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1833,6 +2313,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1843,30 +2324,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -1879,11 +2365,11 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-96808800</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-887880</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
       </c>
@@ -1894,6 +2380,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1902,11 +2389,11 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
@@ -1917,6 +2404,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1925,21 +2413,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-76686000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-26198000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>17875000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>10609000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-41110000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-15752000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1948,21 +2437,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-242022000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-4228000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-435426000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-5431000</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" s="3" t="n">
-        <v>-17469000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1971,21 +2461,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-242022000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-4228000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-435426000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-5431000</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F6" s="3" t="n">
-        <v>-17469000</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1994,21 +2485,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-427634000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-126578000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-455050000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-18370000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-61418000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-29196000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2017,21 +2509,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>30348000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>29589000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>27669000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>19536000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>16259000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>15562000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2040,21 +2533,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>490000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>17039000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>15956000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>21344000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>23868000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>19004000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2063,21 +2557,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-318708000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-30426000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-417551000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>5178000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-41110000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-33221000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2086,21 +2581,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-349056000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-60015000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-445220000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-14358000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-57369000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-48783000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2109,21 +2605,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-37660000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-69942000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-5736000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-4012000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-1790000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-3015000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2132,21 +2629,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>67071000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>62357000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>9830000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>4012000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>4049000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>3015000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2154,16 +2652,19 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n">
+      <c r="B14" s="3" t="n">
+        <v>29411000</v>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n">
         <v>4094000</v>
       </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n">
         <v>2259000</v>
       </c>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n">
         <v>339000</v>
       </c>
     </row>
@@ -2174,21 +2675,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-282420800</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-123237880</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-19624000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-12939000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-61418000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-11727000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2197,21 +2699,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-427634000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-126578000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-455050000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-18370000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-61418000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-29196000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2220,21 +2723,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>170457000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>122470000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>64466000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>57795000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>94033000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>71140000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2243,21 +2747,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-162142000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-86323000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-24672000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-15590000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-59628000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-51424000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2265,18 +2770,21 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n">
+      <c r="B19" s="3" t="n">
+        <v>422999671</v>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n">
         <v>401559291</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>386895095</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>383149511</v>
       </c>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
         <v>382086768</v>
       </c>
     </row>
@@ -2286,18 +2794,21 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n">
+      <c r="B20" s="3" t="n">
+        <v>422999671</v>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
         <v>401559291</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>386895095</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>383149511</v>
       </c>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
         <v>382086768</v>
       </c>
     </row>
@@ -2307,18 +2818,21 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n">
+      <c r="B21" s="3" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
         <v>-1.13</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-0.16</v>
       </c>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2328,18 +2842,21 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n">
+      <c r="B22" s="3" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n">
         <v>-1.13</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-0.16</v>
       </c>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2350,21 +2867,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-427634000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-126578000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-455050000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-18370000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-61418000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-28318000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2373,21 +2891,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-427634000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-126578000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-455050000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-18370000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-61418000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-28318000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2400,7 +2919,8 @@
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n">
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n">
         <v>300000</v>
       </c>
     </row>
@@ -2411,119 +2931,118 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-427634000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-126578000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-455050000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-18370000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-61418000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-29196000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Net Income Including Noncontrolling Interests</t>
+          <t>Minority Interests</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-126578000</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>-455050000</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>-18370000</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>-61418000</v>
-      </c>
+        <v>69000</v>
+      </c>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n">
-        <v>-29196000</v>
+        <v>0</v>
       </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Net Income Discontinuous Operations</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
+          <t>Net Income Including Noncontrolling Interests</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>-427703000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>-126578000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>-455050000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-18370000</v>
+      </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-61418000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Net Income Continuous Operations</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>-126578000</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>-455050000</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>-18370000</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-61418000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>-29196000</v>
-      </c>
-      <c r="G29" s="3" t="n"/>
+          <t>Net Income Discontinuous Operations</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Earnings From Equity Interest Net Of Tax</t>
+          <t>Net Income Continuous Operations</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-4130000</v>
+        <v>-427703000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0</v>
+        <v>-126578000</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0</v>
+        <v>-455050000</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0</v>
+        <v>-18370000</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>22602000</v>
+        <v>-61418000</v>
       </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tax Provision</t>
+          <t>Earnings From Equity Interest Net Of Tax</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>76000</v>
+        <v>-11548000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-4130000</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
@@ -2535,518 +3054,572 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pretax Income</t>
+          <t>Tax Provision</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-122372000</v>
+        <v>28000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-455050000</v>
+        <v>76000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-18370000</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-61418000</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>-51798000</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Other Income Expense</t>
+          <t>Pretax Income</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>34204000</v>
+        <v>-416127000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-435426000</v>
+        <v>-122372000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-4199000</v>
-      </c>
-      <c r="E33" s="3" t="n"/>
+        <v>-455050000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>-18370000</v>
+      </c>
       <c r="F33" s="3" t="n">
-        <v>-12628000</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>-4628000</v>
-      </c>
+        <v>-61418000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Other Non Operating Income Expenses</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
+          <t>Other Income Expense</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>-242022000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>34204000</v>
+      </c>
       <c r="D34" s="3" t="n">
-        <v>1232000</v>
-      </c>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n">
-        <v>4841000</v>
-      </c>
+        <v>-435426000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-4199000</v>
+      </c>
+      <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n">
-        <v>339000</v>
-      </c>
+        <v>-12628000</v>
+      </c>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Special Income Charges</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>923000</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>-10784000</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>-5431000</v>
-      </c>
+          <t>Other Non Operating Income Expenses</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>-17469000</v>
-      </c>
-      <c r="G35" s="3" t="n"/>
+        <v>1232000</v>
+      </c>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n">
+        <v>4841000</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>339000</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gain On Sale Of Ppe</t>
+          <t>Special Income Charges</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-25697000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>923000</v>
       </c>
-      <c r="C36" s="3" t="n">
-        <v>-1987000</v>
-      </c>
       <c r="D36" s="3" t="n">
-        <v>-3831000</v>
-      </c>
-      <c r="E36" s="3" t="n"/>
+        <v>-10784000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>-5431000</v>
+      </c>
       <c r="F36" s="3" t="n">
-        <v>-17824000</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Other Special Charges</t>
+          <t>Gain On Sale Of Ppe</t>
         </is>
       </c>
       <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C37" s="3" t="n">
+        <v>923000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>-1987000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-3831000</v>
+      </c>
+      <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="n">
-        <v>4273000</v>
+        <v>-17824000</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Impairment Of Capital Assets</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>Other Special Charges</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n">
-        <v>-355000</v>
-      </c>
+      <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n">
-        <v>355000</v>
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>4273000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Restructuring And Mergern Acquisition</t>
+          <t>Impairment Of Capital Assets</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0</v>
+        <v>25697000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>8797000</v>
+        <v>0</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1600000</v>
+        <v>0</v>
       </c>
       <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G39" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-355000</v>
+      </c>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gain On Sale Of Security</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>-5151000</v>
-      </c>
+          <t>Restructuring And Mergern Acquisition</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
       <c r="C40" s="3" t="n">
-        <v>-424642000</v>
-      </c>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>8797000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>1600000</v>
+      </c>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Net Non Operating Interest Income Expense</t>
+          <t>Gain On Sale Of Security</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-69942000</v>
+        <v>-216325000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-5736000</v>
+        <v>-5151000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-4012000</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>-1790000</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>-3015000</v>
-      </c>
+        <v>-424642000</v>
+      </c>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Interest Expense Non Operating</t>
+          <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>62357000</v>
+        <v>-37660000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>9830000</v>
+        <v>-69942000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>4012000</v>
+        <v>-5736000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>4049000</v>
+        <v>-4012000</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>3015000</v>
+        <v>-1790000</v>
       </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Interest Income Non Operating</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n"/>
+          <t>Interest Expense Non Operating</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>67071000</v>
+      </c>
       <c r="C43" s="3" t="n">
-        <v>4094000</v>
-      </c>
-      <c r="D43" s="3" t="n"/>
+        <v>62357000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>9830000</v>
+      </c>
       <c r="E43" s="3" t="n">
-        <v>2259000</v>
-      </c>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n">
-        <v>339000</v>
-      </c>
+        <v>4012000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>4049000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t>Interest Income Non Operating</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-86634000</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>-13888000</v>
-      </c>
+        <v>29411000</v>
+      </c>
+      <c r="C44" s="3" t="n"/>
       <c r="D44" s="3" t="n">
-        <v>-10159000</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>-59628000</v>
-      </c>
+        <v>4094000</v>
+      </c>
+      <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n">
-        <v>-36155000</v>
+        <v>2259000</v>
       </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n">
+        <v>339000</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Operating Expense</t>
+          <t>Operating Income</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>103577000</v>
+        <v>-136445000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>47343000</v>
+        <v>-86634000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>35701000</v>
+        <v>-13888000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>69480000</v>
+        <v>-10159000</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>51518000</v>
+        <v>-59628000</v>
       </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Other Operating Expenses</t>
+          <t>Operating Expense</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>9193000</v>
+        <v>168096000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>4165000</v>
+        <v>103577000</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>2627000</v>
+        <v>47343000</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>3762000</v>
+        <v>35701000</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>4299000</v>
+        <v>69480000</v>
       </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion Income Statement</t>
+          <t>Other Operating Expenses</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>27735000</v>
+        <v>11855000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>26502000</v>
+        <v>9193000</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>18786000</v>
+        <v>4165000</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>15574000</v>
+        <v>2627000</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>14944000</v>
+        <v>3762000</v>
       </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization In Income Statement</t>
+          <t>Depreciation Amortization Depletion Income Statement</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>28477000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>27735000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>26502000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>18786000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>15574000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>14944000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Depreciation Income Statement</t>
+          <t>Depreciation And Amortization In Income Statement</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>28477000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>27735000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>26502000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>18786000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>15574000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>14944000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Selling General And Administration</t>
+          <t>Depreciation Income Statement</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>66649000</v>
+        <v>28477000</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>16676000</v>
+        <v>27735000</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>14288000</v>
+        <v>26502000</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>50144000</v>
+        <v>18786000</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>32275000</v>
+        <v>15574000</v>
       </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Selling General And Administration</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>16943000</v>
+        <v>127764000</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>33455000</v>
+        <v>66649000</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>25542000</v>
+        <v>16676000</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>9852000</v>
+        <v>14288000</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>15363000</v>
+        <v>50144000</v>
       </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cost Of Revenue</t>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>18893000</v>
+        <v>31651000</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>17123000</v>
+        <v>16943000</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>22094000</v>
+        <v>33455000</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>24553000</v>
+        <v>25542000</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>19622000</v>
+        <v>9852000</v>
       </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>Cost Of Revenue</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>35836000</v>
+        <v>2361000</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>50578000</v>
+        <v>18893000</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>47636000</v>
+        <v>17123000</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>34405000</v>
+        <v>22094000</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>34985000</v>
+        <v>24553000</v>
       </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>34012000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>35836000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>50578000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>47636000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>34405000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n">
+      <c r="B55" s="3" t="n">
+        <v>34012000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>35836000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>50578000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>47636000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>34405000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>34985000</v>
-      </c>
-      <c r="G54" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4390,7 +4963,1787 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>24468750</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>24468750</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>24468750</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>24468750</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>24468750</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>425050328</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>420065944</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>414745494</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>390130793</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>383729513</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>449519078</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>444534694</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>439214244</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>414599543</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>408198263</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2659956000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1904722000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>348852000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>398723000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>269947000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5314067000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>5195726000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1085265000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>500879000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>491848000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-134231000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>84988000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>182619000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>109602000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>161102000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>5211177000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>5311556000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1298243000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>653775000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>649211000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>482558000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1742425000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>23253000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-52189000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>109120000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-134231000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>84988000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>191884000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>118875000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>170375000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>24116000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>24615000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>25098000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>12163000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>3739000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-78774000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>140445000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>238076000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>165059000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>161102000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Preferred Stock Equity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n">
+        <v>9265000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>9273000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>9273000</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>9273000</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>9273000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>4578686000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>4775473000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1307508000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>663048000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>658484000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-77620000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>140445000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>247341000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>174332000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>170375000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1154000</v>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-78774000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>140445000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>247341000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>174332000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>170375000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>151509000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>151509000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>151509000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>151509000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>151509000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-1421326000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-993692000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-867114000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-412064000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-393694000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1493611000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1285202000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1256260000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>728217000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>705897000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>450000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>444000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>9704000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>9688000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>9681000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>450000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>444000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>439000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>408000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>9265000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>9273000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>9273000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>7086406000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>6417737000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2207104000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>695076000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>670787000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>4701536000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>4681889000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1501253000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>543772000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>549860000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>7888000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>902000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>10876000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1227000</v>
+      </c>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Derivative Product Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n">
+        <v>371603000</v>
+      </c>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>14139000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>23361000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>35504000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>42284000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>58040000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>104000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>76000</v>
+      </c>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>4679509000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>4657626000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1083270000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>500261000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>491820000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>22049000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>22598000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>23103000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>11545000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>3711000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>4657460000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>4635028000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1060167000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>488716000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>488109000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>2384870000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1735848000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>705851000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>151304000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>120927000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1148968000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>844698000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>467945000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>56683000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>58184000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>50653000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>48403000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>31960000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n">
+        <v>687000</v>
+      </c>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>634558000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>538100000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>1995000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>618000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>28000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>2067000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2017000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>1995000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>618000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>28000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>632491000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>536083000</v>
+      </c>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>533918000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>536083000</v>
+      </c>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Line Of Credit</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>98573000</v>
+      </c>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n">
+        <v>1717000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>6216000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>4078000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1512000</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>4552000</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>544661000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>293149000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>179042000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>68205000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>87427000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>316604000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>227810000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>105869000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>29356000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>31955000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>114825000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>52775000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>6868000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>2292000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>5997000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>228057000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>65339000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>73173000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>38849000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>55472000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Dueto Related Parties Current</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>459000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>10892000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>571000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>227598000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>65139000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>62281000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>38834000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>54901000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>7008786000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>6558182000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>2454445000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>869408000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>841162000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>4141358000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>3079909000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1725341000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>770293000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>611115000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>274723000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>274544000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>9996000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>10227000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>8728000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>572774000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>572888000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>572943000</v>
+      </c>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>434793000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>446008000</v>
+      </c>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>79494000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>434793000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>446008000</v>
+      </c>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>79494000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Investmentsin Joint Venturesat Cost</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n">
+        <v>79494000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>55457000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>55457000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>55457000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>55457000</v>
+      </c>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>55457000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>55457000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>55457000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>55457000</v>
+      </c>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>2803611000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1731012000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>1086945000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>704609000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>602387000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>-130905000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>-131752000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>-104263000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-91108000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>-81646000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>2934516000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>1862764000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>1191208000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>795717000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>684033000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>468912000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>265010000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>254740000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>136784000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>119570000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1651299000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1069059000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>409043000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>277946000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>183353000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>554590000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>528126000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>526899000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>380683000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>380989000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>767000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>569000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>526000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>304000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>121000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>16865000</v>
+      </c>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>242083000</v>
+      </c>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>2867428000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>3478273000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>729104000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>99115000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>230047000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>14974000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>11072000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>2919000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>487000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1985000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>196282000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>189933000</v>
+      </c>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>20573000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>6272000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>2955000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>2939000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>4799000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>5604000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>4607000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>11915000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>5696000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>5101000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n">
+        <v>3395000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>8409000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>4524000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>5101000</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>3799000</v>
+      </c>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>5604000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>1212000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>3506000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>1172000</v>
+      </c>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n">
+        <v>475000</v>
+      </c>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>2629995000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>3266389000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>711315000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>89993000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>218162000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>2629995000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>3266389000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>711315000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>89993000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>218162000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5738,13 +8091,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5754,6 +8107,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5764,30 +8118,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5800,21 +8159,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-540545000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-703161000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-268256000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-174752000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-37200000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-196357000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5826,18 +8186,19 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>-12000</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>-33292000</v>
       </c>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5845,22 +8206,23 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n">
         <v>-1000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-9158000</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>-941000</v>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5869,15 +8231,20 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>92750000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>4131364000</v>
       </c>
-      <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>487050000</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5888,7 +8255,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>8956000</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -5903,6 +8270,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5911,21 +8279,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-522954000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-614990000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-231570000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-119942000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-93687000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-153633000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5934,21 +8303,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>5310000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>6880000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>7109000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>2000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5972,6 +8342,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5980,21 +8351,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>3092743000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>3722775000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>712754000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>91418000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>218162000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>274065000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6003,21 +8375,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>3722775000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>712754000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>91418000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>218162000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>274065000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>23938000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6026,21 +8399,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-630032000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>3010021000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>621336000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-126744000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-55903000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>250127000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6049,21 +8423,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>100382000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>4134810000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>858253000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-902000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-51326000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>301614000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6072,21 +8447,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>100382000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>4134810000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>858253000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-902000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-51326000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>301614000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6095,21 +8471,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-5307000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>890000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-111035000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-902000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-18034000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-66893000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6118,19 +8495,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>3983000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>2557000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>3129000</v>
       </c>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F16" s="3" t="n">
-        <v>615000</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>2292000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6138,14 +8518,15 @@
           <t>Net Preferred Stock Issuance</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6153,14 +8534,15 @@
           <t>Preferred Stock Payments</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6169,7 +8551,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0</v>
+        <v>8956000</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>0</v>
@@ -6178,12 +8560,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>-33292000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-118217000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6201,12 +8584,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>-33292000</v>
       </c>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6215,7 +8599,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>8956000</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -6230,6 +8614,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6238,21 +8623,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>92750000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>4131363000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>966171000</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>486109000</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6261,21 +8647,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>92750000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>4131363000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>966171000</v>
       </c>
-      <c r="D23" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>486109000</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6283,22 +8670,23 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n">
         <v>-1000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-9158000</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>-941000</v>
       </c>
-      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6307,15 +8695,20 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>92750000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>4131364000</v>
       </c>
-      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>487050000</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="H25" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6326,21 +8719,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-712823000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-1036618000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-200231000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-71032000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-61064000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-8763000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6349,21 +8743,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-712823000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-1036618000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-200231000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-71032000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-61064000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-8763000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6373,16 +8768,17 @@
       </c>
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n">
         <v>49759000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>32623000</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="G28" s="3" t="n">
         <v>35460000</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="H28" s="3" t="n">
         <v>31911000</v>
       </c>
     </row>
@@ -6394,16 +8790,17 @@
       </c>
       <c r="B29" s="3" t="n"/>
       <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n">
         <v>49759000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>32623000</v>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="G29" s="3" t="n">
         <v>35460000</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="H29" s="3" t="n">
         <v>31911000</v>
       </c>
     </row>
@@ -6414,19 +8811,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-201350000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-450000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-19000000</v>
       </c>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
+      <c r="E30" s="3" t="n">
+        <v>-2731000</v>
+      </c>
       <c r="F30" s="3" t="n">
-        <v>86086000</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6435,19 +8835,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-201350000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-450000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-19000000</v>
       </c>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
+      <c r="E31" s="3" t="n">
+        <v>-2731000</v>
+      </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6456,21 +8859,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>11481000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>25552000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>43393000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>49759000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>32623000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>35460000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6479,21 +8883,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>11481000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>25552000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>43393000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>49759000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>32623000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>35460000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6502,21 +8907,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-522954000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-612170000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-224624000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-118060000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-93687000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-130309000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6524,16 +8930,17 @@
           <t>Sale Of PPE</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n">
         <v>2820000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>6946000</v>
       </c>
-      <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6544,21 +8951,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-522954000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-614990000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-231570000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-119942000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-93687000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-153633000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6567,21 +8975,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-17591000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-88171000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-36686000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>-54810000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>56487000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-42724000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6593,10 +9002,11 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6607,21 +9017,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-17591000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-88171000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-36686000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-54810000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>56487000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-42724000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6630,21 +9041,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>23693000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>3902000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>-11260000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-17183000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>95912000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-5809000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6653,19 +9065,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-10637000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-4633000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-61992000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>687000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>90000000</v>
       </c>
-      <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6674,21 +9089,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>-661000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-10456000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>9393000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-110000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>-6000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-11078000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6697,21 +9113,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-3327000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-11197000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>7750000</v>
       </c>
-      <c r="D43" s="3" t="n">
-        <v>-370000</v>
-      </c>
       <c r="E43" s="3" t="n">
-        <v>-7687000</v>
+        <v>932000</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>-366000</v>
+        <v>-8989000</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6720,21 +9137,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>57122000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>26353000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>39998000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>-16525000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>17213000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>4429000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6743,21 +9161,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>52548000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>23885000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>45874000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>-3276000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>4359000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>3193000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6766,21 +9185,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>4574000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>2468000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-5876000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>-13249000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>12854000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>1236000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6789,21 +9209,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>4315000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>2413000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>-6006000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>-13489000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>13844000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>241000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6812,21 +9233,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>-14301000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>-3317000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>-16000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>-953000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>-2306000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>598000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6835,21 +9257,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>-4503000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>7152000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>-6393000</v>
       </c>
-      <c r="D49" s="3" t="n">
-        <v>88000</v>
-      </c>
       <c r="E49" s="3" t="n">
-        <v>-1302000</v>
+        <v>-1214000</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>608000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6858,17 +9281,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>-4503000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>2138000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>-2508000</v>
       </c>
-      <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n"/>
-      <c r="G50" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E50" s="3" t="n">
+        <v>-544000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6877,21 +9305,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>402000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>-11071000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>-28681000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>-43041000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>-33810000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>-34274000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6900,21 +9329,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>101418000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>6586000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>4345000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>1304000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>38674000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>16746000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6923,21 +9353,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>653000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>967000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>-338000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>-887000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>870000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>-620000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6946,196 +9377,249 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="3" t="n"/>
+        <v>25697000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="D54" s="3" t="n"/>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="n">
         <v>-355000</v>
       </c>
-      <c r="G54" s="3" t="n">
+      <c r="H54" s="3" t="n">
         <v>355000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Deferred Tax</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>29589000</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>27669000</v>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>19536000</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>16259000</v>
-      </c>
+        <v>28000</v>
+      </c>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="n">
-        <v>15562000</v>
+        <v>0</v>
       </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Deferred Income Tax</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>29589000</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>27669000</v>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>19536000</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>16259000</v>
-      </c>
+        <v>28000</v>
+      </c>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n">
-        <v>15562000</v>
+        <v>0</v>
       </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>30348000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>29589000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>27669000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>19536000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>16259000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>15562000</v>
-      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>8358000</v>
+        <v>30348000</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>426629000</v>
-      </c>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="3" t="n"/>
+        <v>29589000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>27669000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>19536000</v>
+      </c>
       <c r="F58" s="3" t="n">
-        <v>-4778000</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>6952000</v>
-      </c>
+        <v>16259000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Earnings Losses From Equity Investments</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>4130000</v>
+        <v>30348000</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0</v>
+        <v>29589000</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0</v>
+        <v>27669000</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0</v>
+        <v>19536000</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0</v>
+        <v>16259000</v>
       </c>
       <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Gain Loss On Investment Securities</t>
+          <t>Operating Gains Losses</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>5151000</v>
-      </c>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
+        <v>227873000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>8358000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>426629000</v>
+      </c>
       <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>-4778000</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>6952000</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Gain Loss On Sale Of PPE</t>
+          <t>Earnings Losses From Equity Investments</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>-923000</v>
+        <v>11548000</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1987000</v>
-      </c>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
+        <v>4130000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F61" s="3" t="n">
-        <v>17824000</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Gain Loss On Investment Securities</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>216325000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>5151000</v>
+      </c>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Gain Loss On Sale Of PPE</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3" t="n">
+        <v>-923000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>1987000</v>
+      </c>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n">
+        <v>17824000</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n">
+      <c r="B64" s="3" t="n">
+        <v>-427703000</v>
+      </c>
+      <c r="C64" s="3" t="n">
         <v>-126578000</v>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="D64" s="3" t="n">
         <v>-455050000</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="E64" s="3" t="n">
         <v>-18370000</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="F64" s="3" t="n">
         <v>-61418000</v>
       </c>
-      <c r="F62" s="3" t="n">
-        <v>-29196000</v>
-      </c>
-      <c r="G62" s="3" t="n"/>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
